--- a/data/trans_bre/P3A_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -6,87</t>
+          <t>-12,49; -7,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -9,33</t>
+          <t>-15,28; -9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -10,24</t>
+          <t>-17,01; -10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -4,74</t>
+          <t>-11,8; -4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,48; -45,75</t>
+          <t>-65,88; -46,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -50,95</t>
+          <t>-68,7; -50,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,79; -51,65</t>
+          <t>-70,44; -51,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -31,34</t>
+          <t>-60,14; -33,18</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -6,71</t>
+          <t>-12,01; -6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -9,7</t>
+          <t>-14,59; -9,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,81; -11,15</t>
+          <t>-16,57; -10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 3,7</t>
+          <t>-10,6; 2,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,41; -33,92</t>
+          <t>-53,93; -33,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,24; -34,88</t>
+          <t>-48,36; -34,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,24; -34,17</t>
+          <t>-46,66; -33,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 11,54</t>
+          <t>-38,99; 9,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,84</t>
+          <t>-7,6; 3,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -2,05</t>
+          <t>-15,18; -1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; -3,12</t>
+          <t>-15,92; -4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -1,22</t>
+          <t>-11,72; -1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 15,68</t>
+          <t>-25,3; 13,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -5,94</t>
+          <t>-37,76; -4,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,08; -8,27</t>
+          <t>-35,46; -10,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,68; -3,14</t>
+          <t>-28,77; -4,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -7,06</t>
+          <t>-10,78; -7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -10,59</t>
+          <t>-14,69; -10,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,81; -11,69</t>
+          <t>-15,89; -11,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -0,58</t>
+          <t>-10,31; -1,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,24; -35,97</t>
+          <t>-48,63; -35,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -40,42</t>
+          <t>-50,99; -39,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,29; -37,24</t>
+          <t>-47,36; -37,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,88; -6,77</t>
+          <t>-36,74; -8,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>-8,14</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-48,04%</t>
+          <t>-48,07%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -7,08</t>
+          <t>-12,57; -7,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -9,46</t>
+          <t>-15,11; -9,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -10,19</t>
+          <t>-16,91; -9,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -4,73</t>
+          <t>-11,5; -4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -46,5</t>
+          <t>-65,94; -45,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,7; -50,27</t>
+          <t>-68,68; -51,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,44; -51,42</t>
+          <t>-70,65; -50,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,14; -33,18</t>
+          <t>-59,7; -32,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,37</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,61%</t>
+          <t>-20,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -6,66</t>
+          <t>-11,84; -6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -9,34</t>
+          <t>-14,65; -9,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -10,77</t>
+          <t>-16,74; -11,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 2,77</t>
+          <t>-8,81; -3,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,93; -33,89</t>
+          <t>-52,36; -33,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,36; -34,17</t>
+          <t>-48,57; -34,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,66; -33,16</t>
+          <t>-47,1; -33,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 9,16</t>
+          <t>-28,21; -11,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,93</t>
+          <t>-8,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-18,26%</t>
+          <t>-21,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 3,38</t>
+          <t>-8,03; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -1,57</t>
+          <t>-15,55; -2,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -4,53</t>
+          <t>-15,99; -4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; -1,68</t>
+          <t>-13,42; -3,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 13,98</t>
+          <t>-26,67; 12,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,76; -4,06</t>
+          <t>-37,9; -6,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,46; -10,95</t>
+          <t>-35,05; -11,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,77; -4,75</t>
+          <t>-32,14; -10,61</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,84</t>
+          <t>-7,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,36%</t>
+          <t>-26,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -7,15</t>
+          <t>-10,64; -7,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -10,71</t>
+          <t>-14,5; -10,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -11,77</t>
+          <t>-16,0; -11,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -1,42</t>
+          <t>-9,65; -5,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,63; -35,34</t>
+          <t>-48,97; -34,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,99; -39,98</t>
+          <t>-50,81; -40,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,36; -37,82</t>
+          <t>-47,6; -37,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -8,18</t>
+          <t>-31,9; -20,69</t>
         </is>
       </c>
     </row>
